--- a/jogos_2025-03-31.xlsx
+++ b/jogos_2025-03-31.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>KF Gostivari</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Voska Sport</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="P2" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>2.61</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['30', '83']</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1.17</v>
       </c>
-      <c r="X2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>['9', '61']</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45747.41666666666</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Besa Dobërdoll</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="N3" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
+        <v>11</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>7</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>4.75</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45747.41666666666</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KF Gostivari</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Voska Sport</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O4" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="P4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>2.92</v>
+        <v>4.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.68</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.56</v>
+        <v>2.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '61']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['30', '83']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45747.41666666666</v>
@@ -1030,16 +1030,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Besa Dobërdoll</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>3.83</v>
       </c>
       <c r="O5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.8</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>11</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AI5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>2.88</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>7</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45747.41666666666</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>3.83</v>
+        <v>6.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
         <v>1.35</v>
@@ -1224,44 +1224,44 @@
         <v>2.74</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="AB6" t="n">
         <v>1.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45747.41666666666</v>
@@ -1278,29 +1278,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ankaragücü</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
         <v>2</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['18', '35', '69']</t>
+          <t>['37', '42']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['24', '76']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45747.45833333334</v>
@@ -1407,29 +1407,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ankaragücü</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X8" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Z8" t="n">
         <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['37', '42']</t>
+          <t>['18', '35', '69']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['24', '76']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45747.45833333334</v>
@@ -2052,35 +2052,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.55</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X13" t="n">
         <v>3.28</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="Y13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA13" t="n">
         <v>3.2</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['22', '36', '71']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['61', '85']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45747.58333333334</v>
@@ -2181,35 +2181,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['4', '39']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45747.58333333334</v>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
@@ -2346,55 +2346,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>1.78</v>
       </c>
       <c r="M15" t="n">
-        <v>3.29</v>
+        <v>3.91</v>
       </c>
       <c r="N15" t="n">
-        <v>2.39</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.4</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AC15" t="n">
         <v>1.57</v>
@@ -2404,25 +2404,25 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['5', '25']</t>
+          <t>['43', '57', '71']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['11', '43']</t>
+          <t>['2', '9']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45747.58333333334</v>
@@ -2439,32 +2439,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.2</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="X16" t="n">
-        <v>4.9</v>
+        <v>3.76</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>3.16</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AI16" t="n">
         <v>1.44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45747.58333333334</v>
@@ -2568,119 +2568,119 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="Z17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['22', '74', '85']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI17" t="n">
         <v>2.1</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['3', '45+3']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45747.58333333334</v>
@@ -2697,32 +2697,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="N18" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X18" t="n">
         <v>3.4</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.35</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.39</v>
+        <v>3.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '39']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['45', '66', '72']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45747.58333333334</v>
@@ -2826,35 +2826,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.77</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.21</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.03</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
-        <v>4.33</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>2.11</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.8</v>
+        <v>2.58</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '45+3']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['77', '90+3']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45747.58333333334</v>
@@ -2955,35 +2955,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['5', '25']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['11', '43']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.73</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45747.58333333334</v>
@@ -3084,35 +3084,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,80 +3120,80 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['33', '50']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.33</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ21" t="n">
         <v>2.38</v>
@@ -3213,35 +3213,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>2.75</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['26']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['22', '74', '85']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.91</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45747.58333333334</v>
@@ -3342,119 +3342,119 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="U23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['22', '36', '71']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['61', '85']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.16</v>
+        <v>1.52</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45747.58333333334</v>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>2.38</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45747.58333333334</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.78</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>3.91</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>2.67</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
         <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.3</v>
@@ -3798,10 +3798,10 @@
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="Y26" t="n">
         <v>1.55</v>
@@ -3816,32 +3816,32 @@
         <v>1.46</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['43', '57', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['2', '9']</t>
+          <t>['45', '66', '72']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45747.58333333334</v>
@@ -3858,35 +3858,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.9</v>
+        <v>3.77</v>
       </c>
       <c r="M27" t="n">
-        <v>3.62</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>3.74</v>
+        <v>2.03</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="X27" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['33', '50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['77', '90+3']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45747.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.69</v>
+        <v>2.98</v>
       </c>
       <c r="M30" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="O30" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R30" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45747.60416666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="N31" t="n">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="O31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T31" t="n">
         <v>3.4</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="X31" t="n">
-        <v>3.28</v>
+        <v>2.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45747.60416666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,19 +4642,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="M33" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="P33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2</v>
-      </c>
       <c r="AA33" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['4', '65']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45747.625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S34" t="n">
         <v>3</v>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>3</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.25</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X34" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['26', '87']</t>
+          <t>['4', '65']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['2', '15', '42', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.66</v>
+        <v>1.03</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.37</v>
+        <v>2.95</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45747.625</v>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T35" t="n">
         <v>2.2</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['37', '63']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.53</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45747.625</v>
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="R36" t="n">
         <v>1.25</v>
@@ -5088,50 +5088,50 @@
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '87']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['37', '63']</t>
+          <t>['2', '15', '42', '56']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45747.625</v>
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,22 +5184,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.77</v>
+        <v>3.23</v>
       </c>
       <c r="M37" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>3.97</v>
+        <v>2.09</v>
       </c>
       <c r="O37" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="R37" t="n">
         <v>1.33</v>
@@ -5208,59 +5208,59 @@
         <v>3.25</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X37" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['17', '56', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['32', '39']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45747.63541666666</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,22 +5313,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.23</v>
+        <v>1.77</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N38" t="n">
-        <v>2.09</v>
+        <v>3.97</v>
       </c>
       <c r="O38" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="R38" t="n">
         <v>1.33</v>
@@ -5337,59 +5337,59 @@
         <v>3.25</v>
       </c>
       <c r="T38" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X38" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AD38" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['17', '56', '90+1']</t>
+          <t>['32', '39']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45747.63541666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.63</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="N39" t="n">
-        <v>2.81</v>
+        <v>3.99</v>
       </c>
       <c r="O39" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P39" t="n">
         <v>1.91</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R39" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S39" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="T39" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X39" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB39" t="n">
         <v>1.2</v>
       </c>
       <c r="AC39" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ39" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45747.64583333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.03</v>
+        <v>2.63</v>
       </c>
       <c r="M41" t="n">
-        <v>3.07</v>
+        <v>2.99</v>
       </c>
       <c r="N41" t="n">
-        <v>3.99</v>
+        <v>2.81</v>
       </c>
       <c r="O41" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
         <v>1.91</v>
       </c>
       <c r="Q41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA41" t="n">
         <v>4.33</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.2</v>
       </c>
       <c r="AB41" t="n">
         <v>1.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45747.64583333334</v>
@@ -5793,35 +5793,35 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3.77</v>
+        <v>3.39</v>
       </c>
       <c r="N42" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O42" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S42" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="U42" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X42" t="n">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="Y42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z42" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD42" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['13', '32', '44', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['82', '90+1']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AJ42" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45747.65625</v>
@@ -5922,26 +5922,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -5950,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="M43" t="n">
-        <v>3.39</v>
+        <v>3.77</v>
       </c>
       <c r="N43" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O43" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="P43" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T43" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X43" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45747.65625</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,22 +6061,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="M44" t="n">
         <v>3.77</v>
       </c>
       <c r="N44" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="P44" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S44" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U44" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.33</v>
       </c>
-      <c r="X44" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC44" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['13', '32', '44', '60']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['82', '90+1']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AJ44" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45747.65625</v>
@@ -6567,35 +6567,35 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wanderers</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
       <c r="O48" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y48" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z48" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['45', '50']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45747.79166666666</v>
@@ -6696,35 +6696,35 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="N49" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P49" t="n">
         <v>1.95</v>
       </c>
-      <c r="O49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q49" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S49" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="T49" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U49" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V49" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W49" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="X49" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="Y49" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['45', '50']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI49" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AJ49" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45747.79166666666</v>
@@ -6964,20 +6964,20 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
         <v>3</v>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="M51" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>3.97</v>
+        <v>3.15</v>
       </c>
       <c r="O51" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="P51" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S51" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="T51" t="n">
-        <v>2.72</v>
+        <v>3.04</v>
       </c>
       <c r="U51" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.22</v>
       </c>
-      <c r="X51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC51" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70', '80', '90+1']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45747.85416666666</v>
@@ -7093,109 +7093,109 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA52" t="n">
         <v>3</v>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U52" t="n">
+      <c r="AB52" t="n">
         <v>1.33</v>
       </c>
-      <c r="V52" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z52" t="n">
+      <c r="AC52" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA52" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD52" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['70', '80', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45747.85416666666</v>
